--- a/stories/arbres/ATOM-REL.AMI.001-11.xlsx
+++ b/stories/arbres/ATOM-REL.AMI.001-11.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Henriette joue au bac à sable. Le sable est frais. Maman est sur le banc. Un camarade arrive. Il s'appelle Noé. Henriette dit : tu veux jouer avec nous ? C'est inviter. Noé secoue la tête. Il dit non. Henriette accepte le non. Elle n'insiste pas. Elle continue le château. Maman dit : tu as su inviter. Tu as su accepter un non. Un non est possible. Plus tard, Léa arrive. Henriette invite encore. Léa dit oui. Elles jouent. Le soir, papa demande. Henriette dit : j'ai invité. Un non, c'est possible aussi. Papa sourit.</t>
+          <t>Henriette joue au bac à sable. Le sable est frais. Maman est sur le banc. Un camarade arrive. Il s'appelle Noé. Tu veux jouer avec nous ? C'est inviter. Noé secoue la tête. Il dit non. Henriette accepte le non. Elle n'insiste pas. Elle continue le château. Tu as su inviter. Tu as su accepter un non. Un non est possible. Plus tard, Léa arrive. Henriette invite encore. Léa dit oui. Elles jouent. Le soir, papa demande. J'ai invité. Un non, c'est possible aussi. Papa sourit.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,17 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Henriette joue au bac à sable. Le sable est frais. Maman est sur le banc. Un camarade arrive. Il s'appelle Noé.
+enfant-f|Tu veux jouer avec nous ? C'est inviter. Noé secoue la tête. Il dit non.
+narrateur|Henriette accepte le non. Elle n'insiste pas. Elle continue le château.
+maman|Tu as su inviter. Tu as su accepter un non.
+narrateur|Un non est possible. Plus tard, Léa arrive. Henriette invite encore. Léa dit oui. Elles jouent. Le soir, papa demande.
+enfant-f|J'ai invité.
+narrateur|Un non, c'est possible aussi. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1492,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Henriette veut jouer. Que dit-elle ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1665,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Henriette a su inviter. Elle a su accepter un non. Maman et papa étaient là.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1795,6 +1832,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Henriette range le seau. Maman lui tend la main.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1957,6 +1999,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1975,7 +2022,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1992,6 +2039,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-REL.AMI.001-11.xlsx
+++ b/stories/arbres/ATOM-REL.AMI.001-11.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1316,6 +1321,7 @@
 narrateur|Un non, c'est possible aussi. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1499,6 +1505,7 @@
           <t>narrateur|Henriette veut jouer. Que dit-elle ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1670,6 +1677,7 @@
           <t>narrateur|Henriette a su inviter. Elle a su accepter un non. Maman et papa étaient là.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1837,6 +1845,7 @@
           <t>narrateur|Henriette range le seau. Maman lui tend la main.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2004,6 +2013,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2022,7 +2032,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2046,6 +2056,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2060,7 +2084,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2247,6 +2271,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-REL.AMI.001-11.xlsx
+++ b/stories/arbres/ATOM-REL.AMI.001-11.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Henriette invite au bac à sable</t>
+          <t>Le château d'Aniss</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Aniss invite Victorina au château de sable. Victorina dit non. Aniss accepte et continue avec maman et papa.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Henriette joue au bac à sable. Le sable est frais. Maman est sur le banc. Un camarade arrive. Il s'appelle Noé. Tu veux jouer avec nous ? C'est inviter. Noé secoue la tête. Il dit non. Henriette accepte le non. Elle n'insiste pas. Elle continue le château. Tu as su inviter. Tu as su accepter un non. Un non est possible. Plus tard, Léa arrive. Henriette invite encore. Léa dit oui. Elles jouent. Le soir, papa demande. J'ai invité. Un non, c'est possible aussi. Papa sourit.</t>
+          <t>Un oiseau pose une ombre sur le sable. L'ombre glisse, puis s'arrête. Le seau rouge est un peu froid. L'écharpe de maman bouge dans l'air. Des grains collent aux chaussures. Ça sent le sable frais. Aniss, tu as vu l'ombre ? C'est l'oiseau, maman. Oui. Il est parti un peu plus loin. En ce moment, Aniss tapote le sable. Il fait un petit château. Le sable est frais sous les paumes. Il a une tour. Une petite tour, d'accord. Je m'assois au banc. Je vous vois bien. Victorina arrive près du bac. Elle a un râteau en bois. Le bois est lisse. Tu peux inviter. Inviter, c'est demander. Tu veux jouer avec nous ? Victorina secoue la tête. Non. Aniss a le ventre un peu serré. Le seau rouge reste près de lui. Maman s'approche du bac. On peut accepter un non. Accepter un non, c'est possible. D'accord. Aniss reste au château. Il continue avec maman. Le sable tombe en petit tas. Tu tapotes bien. La tour tient. Oui. Elle tient. Victorina tire le râteau plus loin. Le râteau fait un bruit doux. Aniss accepte le non. Merci. Tu as su inviter. Tu as su accepter un non. Elle a dit non. Un non, c'est possible aussi. On ajoute du sable ? Oui, papa. L'oiseau passe encore. Son ombre traverse le château. Tu as fini la tour ? Oui. Bravo. Tu as fait du bon travail. Bravo, Aniss. Aniss pose le seau. Le château reste, tout frais.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,16 +1324,70 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Henriette joue au bac à sable. Le sable est frais. Maman est sur le banc. Un camarade arrive. Il s'appelle Noé.
-enfant-f|Tu veux jouer avec nous ? C'est inviter. Noé secoue la tête. Il dit non.
-narrateur|Henriette accepte le non. Elle n'insiste pas. Elle continue le château.
-maman|Tu as su inviter. Tu as su accepter un non.
-narrateur|Un non est possible. Plus tard, Léa arrive. Henriette invite encore. Léa dit oui. Elles jouent. Le soir, papa demande.
-enfant-f|J'ai invité.
-narrateur|Un non, c'est possible aussi. Papa sourit.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+          <t>narrateur|Un oiseau pose une ombre sur le sable.
+narrateur|L'ombre glisse, puis s'arrête.
+narrateur|Le seau rouge est un peu froid.
+narrateur|L'écharpe de maman bouge dans l'air.
+narrateur|Des grains collent aux chaussures.
+narrateur|Ça sent le sable frais.
+maman|Aniss, tu as vu l'ombre ?
+enfant-m|C'est l'oiseau, maman.
+maman|Oui.
+maman|Il est parti un peu plus loin.
+narrateur|En ce moment, Aniss tapote le sable.
+narrateur|Il fait un petit château.
+narrateur|Le sable est frais sous les paumes.
+enfant-m|Il a une tour.
+maman|Une petite tour, d'accord.
+papa|Je m'assois au banc.
+papa|Je vous vois bien.
+narrateur|Victorina arrive près du bac.
+narrateur|Elle a un râteau en bois.
+narrateur|Le bois est lisse.
+maman|Tu peux inviter.
+maman|Inviter, c'est demander.
+enfant-m|Tu veux jouer avec nous ?
+narrateur|Victorina secoue la tête.
+copine|Non.
+narrateur|Aniss a le ventre un peu serré.
+narrateur|Le seau rouge reste près de lui.
+narrateur|Maman s'approche du bac.
+maman|On peut accepter un non.
+maman|Accepter un non, c'est possible.
+enfant-m|D'accord.
+narrateur|Aniss reste au château.
+narrateur|Il continue avec maman.
+narrateur|Le sable tombe en petit tas.
+papa|Tu tapotes bien.
+enfant-m|La tour tient.
+maman|Oui.
+maman|Elle tient.
+narrateur|Victorina tire le râteau plus loin.
+narrateur|Le râteau fait un bruit doux.
+narrateur|Aniss accepte le non.
+maman|Merci.
+maman|Tu as su inviter.
+maman|Tu as su accepter un non.
+enfant-m|Elle a dit non.
+papa|Un non, c'est possible aussi.
+papa|On ajoute du sable ?
+enfant-m|Oui, papa.
+narrateur|L'oiseau passe encore.
+narrateur|Son ombre traverse le château.
+maman|Tu as fini la tour ?
+enfant-m|Oui.
+maman|Bravo.
+maman|Tu as fait du bon travail.
+papa|Bravo, Aniss.
+narrateur|Aniss pose le seau.
+narrateur|Le château reste, tout frais.</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1346,7 +1412,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Henriette veut jouer. Que dit-elle ?</t>
+          <t>Aniss veut jouer. Que dit-il ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1502,10 +1568,10 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Henriette veut jouer. Que dit-elle ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|Aniss veut jouer.
+narrateur|Que dit-il ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1530,7 +1596,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Henriette a su inviter. Elle a su accepter un non. Maman et papa étaient là.</t>
+          <t>Aniss a demandé. C'est inviter. Victorina a dit non. Aniss a accepté le non. Tu as su inviter. Tu as su accepter un non. Bravo, Aniss. J'ai invité. Oui. Un non, c'est possible aussi. Le château reste dans le bac. Le râteau de Victorina est plus loin. Tu as fini le château ? Oui, maman.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1674,10 +1740,22 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Henriette a su inviter. Elle a su accepter un non. Maman et papa étaient là.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Aniss a demandé.
+narrateur|C'est inviter.
+narrateur|Victorina a dit non.
+narrateur|Aniss a accepté le non.
+maman|Tu as su inviter.
+maman|Tu as su accepter un non.
+papa|Bravo, Aniss.
+enfant-m|J'ai invité.
+papa|Oui.
+papa|Un non, c'est possible aussi.
+narrateur|Le château reste dans le bac.
+narrateur|Le râteau de Victorina est plus loin.
+maman|Tu as fini le château ?
+enfant-m|Oui, maman.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1702,7 +1780,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Henriette range le seau. Maman lui tend la main.</t>
+          <t>Aniss range le seau. Des grains tombent sur le chemin. Je prends le seau. Je te tends la main. Elle est chaude. Oui. On rentre. Tu as fini de ranger le seau ? Oui. L'écharpe de maman bouge encore. L'oiseau n'est plus là.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1842,10 +1920,19 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Henriette range le seau. Maman lui tend la main.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Aniss range le seau.
+narrateur|Des grains tombent sur le chemin.
+maman|Je prends le seau.
+papa|Je te tends la main.
+enfant-m|Elle est chaude.
+papa|Oui.
+papa|On rentre.
+maman|Tu as fini de ranger le seau ?
+enfant-m|Oui.
+narrateur|L'écharpe de maman bouge encore.
+narrateur|L'oiseau n'est plus là.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1870,7 +1957,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Aniss a invité. Il a accepté un non. Le château reste au parc. Tu as invité, ce soir. J'ai invité. Un non, c'est possible aussi. Bravo, Aniss. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2010,10 +2097,16 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>narrateur|Aniss a invité.
+narrateur|Il a accepté un non.
+narrateur|Le château reste au parc.
+papa|Tu as invité, ce soir.
+enfant-m|J'ai invité.
+maman|Un non, c'est possible aussi.
+papa|Bravo, Aniss.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2032,7 +2125,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2070,6 +2163,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-REL.AMI.001-11.xlsx
+++ b/stories/arbres/ATOM-REL.AMI.001-11.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Un oiseau pose une ombre sur le sable. L'ombre glisse, puis s'arrête. Le seau rouge est un peu froid. L'écharpe de maman bouge dans l'air. Des grains collent aux chaussures. Ça sent le sable frais. Aniss, tu as vu l'ombre ? C'est l'oiseau, maman. Oui. Il est parti un peu plus loin. En ce moment, Aniss tapote le sable. Il fait un petit château. Le sable est frais sous les paumes. Il a une tour. Une petite tour, d'accord. Je m'assois au banc. Je vous vois bien. Victorina arrive près du bac. Elle a un râteau en bois. Le bois est lisse. Tu peux inviter. Inviter, c'est demander. Tu veux jouer avec nous ? Victorina secoue la tête. Non. Aniss a le ventre un peu serré. Le seau rouge reste près de lui. Maman s'approche du bac. On peut accepter un non. Accepter un non, c'est possible. D'accord. Aniss reste au château. Il continue avec maman. Le sable tombe en petit tas. Tu tapotes bien. La tour tient. Oui. Elle tient. Victorina tire le râteau plus loin. Le râteau fait un bruit doux. Aniss accepte le non. Merci. Tu as su inviter. Tu as su accepter un non. Elle a dit non. Un non, c'est possible aussi. On ajoute du sable ? Oui, papa. L'oiseau passe encore. Son ombre traverse le château. Tu as fini la tour ? Oui. Bravo. Tu as fait du bon travail. Bravo, Aniss. Aniss pose le seau. Le château reste, tout frais.</t>
+          <t>Un oiseau pose une ombre sur le sable. L'ombre glisse, puis s'arrête. Le seau rouge est un peu froid. L'écharpe de maman bouge dans l'air. Des grains collent aux chaussures. Ça sent le sable frais. Aniss, tu as vu l'ombre ? C'est l'oiseau, maman. Oui. Il est parti un peu plus loin. En ce moment, Aniss tapote le sable. Il fait un petit château. Le sable est frais sous les paumes. Il a une tour. Une petite tour, d'accord. Je m'assois au banc. Je vous vois bien. Victorina arrive près du bac. Elle a un râteau en bois. Le bois est lisse. Tu peux inviter. Inviter, c'est demander. Tu veux jouer avec nous ? Victorina secoue la tête. Non. Aniss a le ventre un peu serré. Le seau rouge reste près de lui. Maman s'approche du bac. On peut accepter un non. Accepter un non, c'est possible. D'accord. Aniss reste au château. Il continue avec maman. Le sable tombe en petit tas. Tu tapotes bien. La tour tient. Oui. Elle tient. Victorina tire le râteau plus loin. Le râteau fait un bruit doux. Aniss accepte le non. Merci. Tu as su inviter. Tu as su accepter un non. Elle a dit non. Un non, c'est possible aussi. On ajoute du sable ? Oui, papa. L'oiseau passe encore. Son ombre traverse le château. Tu as fini la tour ? Oui. Bravo. Bravo, Aniss. Aniss pose le seau. Le château reste, tout frais.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Henriette joue au bac à sable. Le sable est frais. Maman est sur le banc. Un camarade arrive. Il s'appelle Noé. Henriette dit : tu veux jouer avec nous ? C'est &lt;emphasis level="moderate"&gt;inviter&lt;/emphasis&gt;. Noé secoue la tête. Il dit non. Henriette accepte le non. Elle n'insiste pas. Elle continue le château. Maman dit : tu as su inviter. Tu as su accepter un non. Un non est possible. Plus tard, Léa arrive. Henriette invite encore. Léa dit oui. Elles jouent. Le soir, papa demande. Henriette dit : j'ai invité. Un non, c'est possible aussi. Papa sourit.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Un oiseau pose une ombre sur le sable. L'ombre glisse, puis s'arrête. Le seau rouge est un peu froid. L'écharpe de maman bouge dans l'air. Des grains collent aux chaussures. Ça sent le sable frais. Aniss, tu as vu l'ombre ? C'est l'oiseau, maman. Oui. Il est parti un peu plus loin. En ce moment, Aniss tapote le sable. Il fait un petit château. Le sable est frais sous les paumes. Il a une tour. Une petite tour, d'accord. Je m'assois au banc. Je vous vois bien. Victorina arrive près du bac. Elle a un râteau en bois. Le bois est lisse. Tu peux inviter. Inviter, c'est demander. Tu veux jouer avec nous ? Victorina secoue la tête. Non. Aniss a le ventre un peu serré. Le seau rouge reste près de lui. Maman s'approche du bac. On peut accepter un non. Accepter un non, c'est possible. D'accord. Aniss reste au château. Il continue avec maman. Le sable tombe en petit tas. Tu tapotes bien. La tour tient. Oui. Elle tient. Victorina tire le râteau plus loin. Le râteau fait un bruit doux. Aniss accepte le non. Merci. Tu as su inviter. Tu as su accepter un non. Elle a dit non. Un non, c'est possible aussi. On ajoute du sable ? Oui, papa. L'oiseau passe encore. Son ombre traverse le château. Tu as fini la tour ? Oui. Bravo. Bravo, Aniss. Aniss pose le seau. Le château reste, tout frais.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1377,7 +1377,6 @@
 maman|Tu as fini la tour ?
 enfant-m|Oui.
 maman|Bravo.
-maman|Tu as fait du bon travail.
 papa|Bravo, Aniss.
 narrateur|Aniss pose le seau.
 narrateur|Le château reste, tout frais.</t>
@@ -1417,7 +1416,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Henriette veut jouer. Que dit-elle ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Aniss veut jouer. Que dit-il ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1601,7 +1600,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Henriette a su &lt;emphasis level="moderate"&gt;inviter&lt;/emphasis&gt;. Elle a su accepter un non. Maman et papa étaient là.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Aniss a demandé. C'est inviter. Victorina a dit non. Aniss a accepté le non. Tu as su inviter. Tu as su accepter un non. Bravo, Aniss. J'ai invité. Oui. Un non, c'est possible aussi. Le château reste dans le bac. Le râteau de Victorina est plus loin. Tu as fini le château ? Oui, maman.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1785,7 +1784,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Henriette range le seau. Maman lui tend la &lt;emphasis level="moderate"&gt;main&lt;/emphasis&gt;.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Aniss range le seau. Des grains tombent sur le chemin. Je prends le seau. Je te tends la main. Elle est chaude. Oui. On rentre. Tu as fini de ranger le seau ? Oui. L'écharpe de maman bouge encore. L'oiseau n'est plus là.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1957,12 +1956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Aniss a invité. Il a accepté un non. Le château reste au parc. Tu as invité, ce soir. J'ai invité. Un non, c'est possible aussi. Bravo, Aniss. L'histoire est finie.</t>
+          <t>Aniss a invité. Il a accepté un non. Le château reste au parc. Tu as invité, ce soir. J'ai invité. Un non, c'est possible aussi. Bravo, Aniss.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Aniss a invité. Il a accepté un non. Le château reste au parc. Tu as invité, ce soir. J'ai invité. Un non, c'est possible aussi. Bravo, Aniss.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2103,8 +2102,7 @@
 papa|Tu as invité, ce soir.
 enfant-m|J'ai invité.
 maman|Un non, c'est possible aussi.
-papa|Bravo, Aniss.
-narrateur|L'histoire est finie.</t>
+papa|Bravo, Aniss.</t>
         </is>
       </c>
     </row>
@@ -2125,7 +2123,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2170,6 +2168,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-REL.AMI.001-11.xlsx
+++ b/stories/arbres/ATOM-REL.AMI.001-11.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Henriette, maman, papa</t>
+          <t>Aniss, Victorina, maman, papa</t>
         </is>
       </c>
     </row>
